--- a/query_results.xlsx
+++ b/query_results.xlsx
@@ -425,303 +425,552 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>discount</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>order_date</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>order_priority</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>segment</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>ship_date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ship_mode</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>shipping_cost</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>sub_category</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
           <t>order_year</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>order_month</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>order_quarter</t>
+          <t>rolling_avg</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>order_day_of_week</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>is_weekend</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>order_week</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>discount_bin</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>profit_margin</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>sales_per_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Office Supplies</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Arlington</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MZ-175154</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mary Zewe</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Us</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="A2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2013-06-12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CA-2013-169922</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>OFF-BI-10003784</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Computer Printout Index Tabs</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>-2.1504</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="C2" t="n">
+        <v>98902</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>95027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>111926.6666666667</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
+      <c r="C5" t="n">
+        <v>117935</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>136471.6666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>159634.3333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>159164.6666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>179434</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>204439.3333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>232290</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>262599.6666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>277170</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2013-06-18</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Standard Class</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Binders</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="C14" t="n">
+        <v>256071.6666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>190079</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>133129.3333333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>141557.6666666667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>177507.3333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="C19" t="n">
+        <v>208537</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>203266</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>234862</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>245931.6666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>281830</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>288614.6666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>304899.6666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>286984.6666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B27" t="n">
         <v>2</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="C27" t="n">
+        <v>234896.3333333333</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>188345</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>181224.3333333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>212317</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>278291</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>295659.3333333333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>317648</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>311019</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" t="n">
+        <v>332180</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>348015</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" t="n">
+        <v>357631.6666666667</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>340246.3333333333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>30%+</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>-215.04</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.25</v>
+      <c r="C39" t="n">
+        <v>277197</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>229741.6666666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>230246.3333333333</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>264765</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>311009.3333333333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>316321.6666666667</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>372398</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>398845.6666666667</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="n">
+        <v>453534.6666666667</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="n">
+        <v>486427.6666666667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" t="n">
+        <v>493750.3333333333</v>
       </c>
     </row>
   </sheetData>
